--- a/informes_data/Segunda FEB/2026-27/Regular_Season/aggregate_individual/AGG_IND_C.B. STARLABS MORÓN.xlsx
+++ b/informes_data/Segunda FEB/2026-27/Regular_Season/aggregate_individual/AGG_IND_C.B. STARLABS MORÓN.xlsx
@@ -413,7 +413,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:X13"/>
+  <dimension ref="A1:X12"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -697,7 +697,7 @@
     <row r="4">
       <c r="A4" t="inlineStr">
         <is>
-          <t>J. JIMÉNEZ GONZÁLEZ</t>
+          <t>P. SANCHEZ INFANTES</t>
         </is>
       </c>
       <c r="B4" t="inlineStr">
@@ -709,73 +709,73 @@
         <v>4</v>
       </c>
       <c r="D4" t="n">
-        <v>5.7827</v>
+        <v>2.7671</v>
       </c>
       <c r="E4" t="n">
-        <v>5.7827</v>
+        <v>6.4736</v>
       </c>
       <c r="F4" t="n">
-        <v>0</v>
+        <v>-3.7063</v>
       </c>
       <c r="G4" t="n">
-        <v>5.7827</v>
+        <v>8.985700000000001</v>
       </c>
       <c r="H4" t="n">
-        <v>0.9225</v>
+        <v>-4.6703</v>
       </c>
       <c r="I4" t="n">
-        <v>4.8601</v>
+        <v>13.656</v>
       </c>
       <c r="J4" t="n">
-        <v>5.7827</v>
+        <v>13.6643</v>
       </c>
       <c r="K4" t="n">
-        <v>0.9225</v>
+        <v>-0.4702</v>
       </c>
       <c r="L4" t="n">
-        <v>4.8601</v>
+        <v>14.1345</v>
       </c>
       <c r="M4" t="n">
-        <v>0</v>
+        <v>-4.6788</v>
       </c>
       <c r="N4" t="n">
-        <v>0</v>
+        <v>-4.2001</v>
       </c>
       <c r="O4" t="n">
-        <v>0</v>
+        <v>-0.4785</v>
       </c>
       <c r="P4" t="n">
-        <v>0</v>
+        <v>-10.7241</v>
       </c>
       <c r="Q4" t="n">
-        <v>0</v>
+        <v>-15.7938</v>
       </c>
       <c r="R4" t="n">
-        <v>0</v>
+        <v>5.0696</v>
       </c>
       <c r="S4" t="n">
-        <v>0</v>
+        <v>-0.9106000000000001</v>
       </c>
       <c r="T4" t="n">
-        <v>0</v>
+        <v>-0.4416</v>
       </c>
       <c r="U4" t="n">
-        <v>0</v>
+        <v>-0.4689</v>
       </c>
       <c r="V4" t="n">
-        <v>0</v>
+        <v>5.4161</v>
       </c>
       <c r="W4" t="n">
-        <v>0</v>
+        <v>9.044599999999999</v>
       </c>
       <c r="X4" t="n">
-        <v>0</v>
+        <v>-3.6285</v>
       </c>
     </row>
     <row r="5">
       <c r="A5" t="inlineStr">
         <is>
-          <t>P. SANCHEZ INFANTES</t>
+          <t>M. AYESA RODRIGUEZ</t>
         </is>
       </c>
       <c r="B5" t="inlineStr">
@@ -787,73 +787,73 @@
         <v>4</v>
       </c>
       <c r="D5" t="n">
-        <v>2.7671</v>
+        <v>2.6577</v>
       </c>
       <c r="E5" t="n">
-        <v>6.4736</v>
+        <v>7.1669</v>
       </c>
       <c r="F5" t="n">
-        <v>-3.7063</v>
+        <v>-4.5093</v>
       </c>
       <c r="G5" t="n">
-        <v>8.985700000000001</v>
+        <v>4.584300000000001</v>
       </c>
       <c r="H5" t="n">
-        <v>-4.6703</v>
+        <v>-2.4704</v>
       </c>
       <c r="I5" t="n">
-        <v>13.656</v>
+        <v>7.0548</v>
       </c>
       <c r="J5" t="n">
-        <v>13.6643</v>
+        <v>9.597300000000001</v>
       </c>
       <c r="K5" t="n">
-        <v>-0.4702</v>
+        <v>1.2474</v>
       </c>
       <c r="L5" t="n">
-        <v>14.1345</v>
+        <v>8.3499</v>
       </c>
       <c r="M5" t="n">
-        <v>-4.6788</v>
+        <v>-5.013</v>
       </c>
       <c r="N5" t="n">
-        <v>-4.2001</v>
+        <v>-3.7178</v>
       </c>
       <c r="O5" t="n">
-        <v>-0.4785</v>
+        <v>-1.2951</v>
       </c>
       <c r="P5" t="n">
-        <v>-10.7241</v>
+        <v>1.9499</v>
       </c>
       <c r="Q5" t="n">
-        <v>-15.7938</v>
+        <v>-2.9248</v>
       </c>
       <c r="R5" t="n">
-        <v>5.0696</v>
+        <v>4.8746</v>
       </c>
       <c r="S5" t="n">
-        <v>-0.9106000000000001</v>
+        <v>-1.2426</v>
       </c>
       <c r="T5" t="n">
-        <v>-0.4416</v>
+        <v>-0.7257</v>
       </c>
       <c r="U5" t="n">
-        <v>-0.4689</v>
+        <v>-0.5168999999999999</v>
       </c>
       <c r="V5" t="n">
-        <v>5.4161</v>
+        <v>-2.6341</v>
       </c>
       <c r="W5" t="n">
-        <v>9.044599999999999</v>
+        <v>1.2201</v>
       </c>
       <c r="X5" t="n">
-        <v>-3.6285</v>
+        <v>-3.8541</v>
       </c>
     </row>
     <row r="6">
       <c r="A6" t="inlineStr">
         <is>
-          <t>M. AYESA RODRIGUEZ</t>
+          <t>A. DIEYE</t>
         </is>
       </c>
       <c r="B6" t="inlineStr">
@@ -865,73 +865,73 @@
         <v>4</v>
       </c>
       <c r="D6" t="n">
-        <v>2.6577</v>
+        <v>2.3886</v>
       </c>
       <c r="E6" t="n">
-        <v>7.1669</v>
+        <v>0.2161000000000004</v>
       </c>
       <c r="F6" t="n">
-        <v>-4.5093</v>
+        <v>2.1725</v>
       </c>
       <c r="G6" t="n">
-        <v>4.584300000000001</v>
+        <v>0.1219999999999999</v>
       </c>
       <c r="H6" t="n">
-        <v>-2.4704</v>
+        <v>-0.3154999999999997</v>
       </c>
       <c r="I6" t="n">
-        <v>7.0548</v>
+        <v>0.4374999999999999</v>
       </c>
       <c r="J6" t="n">
-        <v>9.597300000000001</v>
+        <v>1.4206</v>
       </c>
       <c r="K6" t="n">
-        <v>1.2474</v>
+        <v>1.8259</v>
       </c>
       <c r="L6" t="n">
-        <v>8.3499</v>
+        <v>-0.4055</v>
       </c>
       <c r="M6" t="n">
-        <v>-5.013</v>
+        <v>-1.2985</v>
       </c>
       <c r="N6" t="n">
-        <v>-3.7178</v>
+        <v>-2.1415</v>
       </c>
       <c r="O6" t="n">
-        <v>-1.2951</v>
+        <v>0.843</v>
       </c>
       <c r="P6" t="n">
-        <v>1.9499</v>
+        <v>0.1950000000000001</v>
       </c>
       <c r="Q6" t="n">
-        <v>-2.9248</v>
+        <v>-4.8746</v>
       </c>
       <c r="R6" t="n">
-        <v>4.8746</v>
+        <v>5.0696</v>
       </c>
       <c r="S6" t="n">
-        <v>-1.2426</v>
+        <v>1.9518</v>
       </c>
       <c r="T6" t="n">
-        <v>-0.7257</v>
+        <v>2.1047</v>
       </c>
       <c r="U6" t="n">
-        <v>-0.5168999999999999</v>
+        <v>-0.1529</v>
       </c>
       <c r="V6" t="n">
-        <v>-2.6341</v>
+        <v>0.1197000000000001</v>
       </c>
       <c r="W6" t="n">
-        <v>1.2201</v>
+        <v>1.5656</v>
       </c>
       <c r="X6" t="n">
-        <v>-3.8541</v>
+        <v>-1.4457</v>
       </c>
     </row>
     <row r="7">
       <c r="A7" t="inlineStr">
         <is>
-          <t>A. DIEYE</t>
+          <t>A. OROZCO DOMINGUEZ</t>
         </is>
       </c>
       <c r="B7" t="inlineStr">
@@ -943,73 +943,73 @@
         <v>4</v>
       </c>
       <c r="D7" t="n">
-        <v>2.3886</v>
+        <v>2.0026</v>
       </c>
       <c r="E7" t="n">
-        <v>0.2161000000000004</v>
+        <v>1.5459</v>
       </c>
       <c r="F7" t="n">
-        <v>2.1725</v>
+        <v>0.4567</v>
       </c>
       <c r="G7" t="n">
-        <v>0.1219999999999999</v>
+        <v>-1.5248</v>
       </c>
       <c r="H7" t="n">
-        <v>-0.3154999999999997</v>
+        <v>-1.257</v>
       </c>
       <c r="I7" t="n">
-        <v>0.4374999999999999</v>
+        <v>-0.2677999999999998</v>
       </c>
       <c r="J7" t="n">
-        <v>1.4206</v>
+        <v>1.126300000000001</v>
       </c>
       <c r="K7" t="n">
-        <v>1.8259</v>
+        <v>1.4271</v>
       </c>
       <c r="L7" t="n">
-        <v>-0.4055</v>
+        <v>-0.3008000000000002</v>
       </c>
       <c r="M7" t="n">
-        <v>-1.2985</v>
+        <v>-2.6512</v>
       </c>
       <c r="N7" t="n">
-        <v>-2.1415</v>
+        <v>-2.6841</v>
       </c>
       <c r="O7" t="n">
-        <v>0.843</v>
+        <v>0.03300000000000003</v>
       </c>
       <c r="P7" t="n">
-        <v>0.1950000000000001</v>
+        <v>1.9498</v>
       </c>
       <c r="Q7" t="n">
-        <v>-4.8746</v>
+        <v>-3.1198</v>
       </c>
       <c r="R7" t="n">
-        <v>5.0696</v>
+        <v>5.069599999999999</v>
       </c>
       <c r="S7" t="n">
-        <v>1.9518</v>
+        <v>0.3393</v>
       </c>
       <c r="T7" t="n">
-        <v>2.1047</v>
+        <v>1.4308</v>
       </c>
       <c r="U7" t="n">
-        <v>-0.1529</v>
+        <v>-1.0914</v>
       </c>
       <c r="V7" t="n">
-        <v>0.1197000000000001</v>
+        <v>1.2384</v>
       </c>
       <c r="W7" t="n">
-        <v>1.5656</v>
+        <v>2.1087</v>
       </c>
       <c r="X7" t="n">
-        <v>-1.4457</v>
+        <v>-0.8702000000000001</v>
       </c>
     </row>
     <row r="8">
       <c r="A8" t="inlineStr">
         <is>
-          <t>A. OROZCO DOMINGUEZ</t>
+          <t>J. JIMENEZ GONZALEZ</t>
         </is>
       </c>
       <c r="B8" t="inlineStr">
@@ -1021,67 +1021,67 @@
         <v>4</v>
       </c>
       <c r="D8" t="n">
-        <v>2.0026</v>
+        <v>0.1163000000000007</v>
       </c>
       <c r="E8" t="n">
-        <v>1.5459</v>
+        <v>1.1585</v>
       </c>
       <c r="F8" t="n">
-        <v>0.4567</v>
+        <v>-1.0422</v>
       </c>
       <c r="G8" t="n">
-        <v>-1.5248</v>
+        <v>-1.992100000000001</v>
       </c>
       <c r="H8" t="n">
-        <v>-1.257</v>
+        <v>-2.9831</v>
       </c>
       <c r="I8" t="n">
-        <v>-0.2677999999999998</v>
+        <v>0.9909000000000003</v>
       </c>
       <c r="J8" t="n">
-        <v>1.126300000000001</v>
+        <v>2.1305</v>
       </c>
       <c r="K8" t="n">
-        <v>1.4271</v>
+        <v>-0.2816999999999998</v>
       </c>
       <c r="L8" t="n">
-        <v>-0.3008000000000002</v>
+        <v>2.412199999999999</v>
       </c>
       <c r="M8" t="n">
-        <v>-2.6512</v>
+        <v>-4.1226</v>
       </c>
       <c r="N8" t="n">
-        <v>-2.6841</v>
+        <v>-2.7014</v>
       </c>
       <c r="O8" t="n">
-        <v>0.03300000000000003</v>
+        <v>-1.4213</v>
       </c>
       <c r="P8" t="n">
-        <v>1.9498</v>
+        <v>0.9748999999999999</v>
       </c>
       <c r="Q8" t="n">
-        <v>-3.1198</v>
+        <v>-6.2395</v>
       </c>
       <c r="R8" t="n">
-        <v>5.069599999999999</v>
+        <v>7.2144</v>
       </c>
       <c r="S8" t="n">
-        <v>0.3393</v>
+        <v>0.1602999999999999</v>
       </c>
       <c r="T8" t="n">
-        <v>1.4308</v>
+        <v>0.1616</v>
       </c>
       <c r="U8" t="n">
-        <v>-1.0914</v>
+        <v>-0.001299999999999968</v>
       </c>
       <c r="V8" t="n">
-        <v>1.2384</v>
+        <v>0.9733000000000001</v>
       </c>
       <c r="W8" t="n">
-        <v>2.1087</v>
+        <v>5.1059</v>
       </c>
       <c r="X8" t="n">
-        <v>-0.8702000000000001</v>
+        <v>-4.1326</v>
       </c>
     </row>
     <row r="9">
@@ -1243,7 +1243,7 @@
     <row r="11">
       <c r="A11" t="inlineStr">
         <is>
-          <t>J. JIMENEZ GONZALEZ</t>
+          <t>J. PLEASANT</t>
         </is>
       </c>
       <c r="B11" t="inlineStr">
@@ -1255,73 +1255,73 @@
         <v>4</v>
       </c>
       <c r="D11" t="n">
-        <v>-5.666399999999999</v>
+        <v>-11.1065</v>
       </c>
       <c r="E11" t="n">
-        <v>-4.624199999999999</v>
+        <v>-10.8126</v>
       </c>
       <c r="F11" t="n">
-        <v>-1.0422</v>
+        <v>-0.2938999999999999</v>
       </c>
       <c r="G11" t="n">
-        <v>-7.7749</v>
+        <v>-13.993</v>
       </c>
       <c r="H11" t="n">
-        <v>-3.9056</v>
+        <v>-11.2535</v>
       </c>
       <c r="I11" t="n">
-        <v>-3.8693</v>
+        <v>-2.739400000000001</v>
       </c>
       <c r="J11" t="n">
-        <v>-3.652200000000001</v>
+        <v>-8.984999999999999</v>
       </c>
       <c r="K11" t="n">
-        <v>-1.2042</v>
+        <v>-8.214500000000001</v>
       </c>
       <c r="L11" t="n">
-        <v>-2.447900000000001</v>
+        <v>-0.7704000000000004</v>
       </c>
       <c r="M11" t="n">
-        <v>-4.1226</v>
+        <v>-5.0081</v>
       </c>
       <c r="N11" t="n">
-        <v>-2.7014</v>
+        <v>-3.0391</v>
       </c>
       <c r="O11" t="n">
-        <v>-1.4213</v>
+        <v>-1.969</v>
       </c>
       <c r="P11" t="n">
-        <v>0.9748999999999999</v>
+        <v>1.5599</v>
       </c>
       <c r="Q11" t="n">
-        <v>-6.2395</v>
+        <v>-4.2897</v>
       </c>
       <c r="R11" t="n">
-        <v>7.2144</v>
+        <v>5.8496</v>
       </c>
       <c r="S11" t="n">
-        <v>0.1602999999999999</v>
+        <v>-0.1691000000000001</v>
       </c>
       <c r="T11" t="n">
-        <v>0.1616</v>
+        <v>0.4062</v>
       </c>
       <c r="U11" t="n">
-        <v>-0.001299999999999968</v>
+        <v>-0.5755</v>
       </c>
       <c r="V11" t="n">
-        <v>0.9733000000000001</v>
+        <v>1.4958</v>
       </c>
       <c r="W11" t="n">
-        <v>5.1059</v>
+        <v>2.0558</v>
       </c>
       <c r="X11" t="n">
-        <v>-4.1326</v>
+        <v>-0.5600000000000001</v>
       </c>
     </row>
     <row r="12">
       <c r="A12" t="inlineStr">
         <is>
-          <t>J. PLEASANT</t>
+          <t>--- TOTAL ---</t>
         </is>
       </c>
       <c r="B12" t="inlineStr">
@@ -1333,144 +1333,66 @@
         <v>4</v>
       </c>
       <c r="D12" t="n">
-        <v>-11.1065</v>
+        <v>9.046399999999995</v>
       </c>
       <c r="E12" t="n">
-        <v>-10.8126</v>
+        <v>22.8183</v>
       </c>
       <c r="F12" t="n">
-        <v>-0.2938999999999999</v>
+        <v>-13.7717</v>
       </c>
       <c r="G12" t="n">
-        <v>-13.993</v>
+        <v>2.757900000000001</v>
       </c>
       <c r="H12" t="n">
-        <v>-11.2535</v>
+        <v>-21.5266</v>
       </c>
       <c r="I12" t="n">
-        <v>-2.739400000000001</v>
+        <v>24.2847</v>
       </c>
       <c r="J12" t="n">
-        <v>-8.984999999999999</v>
+        <v>36.3147</v>
       </c>
       <c r="K12" t="n">
-        <v>-8.214500000000001</v>
+        <v>5.038999999999998</v>
       </c>
       <c r="L12" t="n">
-        <v>-0.7704000000000004</v>
+        <v>31.27569999999999</v>
       </c>
       <c r="M12" t="n">
-        <v>-5.0081</v>
+        <v>-33.557</v>
       </c>
       <c r="N12" t="n">
-        <v>-3.0391</v>
+        <v>-26.5656</v>
       </c>
       <c r="O12" t="n">
-        <v>-1.969</v>
+        <v>-6.991000000000001</v>
       </c>
       <c r="P12" t="n">
-        <v>1.5599</v>
+        <v>-1.949699999999999</v>
       </c>
       <c r="Q12" t="n">
-        <v>-4.2897</v>
+        <v>-52.64609999999999</v>
       </c>
       <c r="R12" t="n">
-        <v>5.8496</v>
+        <v>50.6962</v>
       </c>
       <c r="S12" t="n">
-        <v>-0.1691000000000001</v>
+        <v>4.193999999999999</v>
       </c>
       <c r="T12" t="n">
-        <v>0.4062</v>
+        <v>8.831900000000001</v>
       </c>
       <c r="U12" t="n">
-        <v>-0.5755</v>
+        <v>-4.6378</v>
       </c>
       <c r="V12" t="n">
-        <v>1.4958</v>
+        <v>4.044300000000001</v>
       </c>
       <c r="W12" t="n">
-        <v>2.0558</v>
+        <v>30.3183</v>
       </c>
       <c r="X12" t="n">
-        <v>-0.5600000000000001</v>
-      </c>
-    </row>
-    <row r="13">
-      <c r="A13" t="inlineStr">
-        <is>
-          <t>--- TOTAL ---</t>
-        </is>
-      </c>
-      <c r="B13" t="inlineStr">
-        <is>
-          <t>C.B. STARLABS MORÓN</t>
-        </is>
-      </c>
-      <c r="C13" t="n">
-        <v>4</v>
-      </c>
-      <c r="D13" t="n">
-        <v>9.046399999999991</v>
-      </c>
-      <c r="E13" t="n">
-        <v>22.8183</v>
-      </c>
-      <c r="F13" t="n">
-        <v>-13.7717</v>
-      </c>
-      <c r="G13" t="n">
-        <v>2.757800000000001</v>
-      </c>
-      <c r="H13" t="n">
-        <v>-21.5266</v>
-      </c>
-      <c r="I13" t="n">
-        <v>24.2846</v>
-      </c>
-      <c r="J13" t="n">
-        <v>36.31469999999999</v>
-      </c>
-      <c r="K13" t="n">
-        <v>5.038999999999998</v>
-      </c>
-      <c r="L13" t="n">
-        <v>31.27569999999999</v>
-      </c>
-      <c r="M13" t="n">
-        <v>-33.557</v>
-      </c>
-      <c r="N13" t="n">
-        <v>-26.5656</v>
-      </c>
-      <c r="O13" t="n">
-        <v>-6.991000000000001</v>
-      </c>
-      <c r="P13" t="n">
-        <v>-1.949699999999999</v>
-      </c>
-      <c r="Q13" t="n">
-        <v>-52.6461</v>
-      </c>
-      <c r="R13" t="n">
-        <v>50.6962</v>
-      </c>
-      <c r="S13" t="n">
-        <v>4.194</v>
-      </c>
-      <c r="T13" t="n">
-        <v>8.831900000000001</v>
-      </c>
-      <c r="U13" t="n">
-        <v>-4.637799999999999</v>
-      </c>
-      <c r="V13" t="n">
-        <v>4.044300000000001</v>
-      </c>
-      <c r="W13" t="n">
-        <v>30.3183</v>
-      </c>
-      <c r="X13" t="n">
         <v>-26.2737</v>
       </c>
     </row>
